--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxfu\OneDrive\Documents\CatanData\catan_data\catan_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB34D29-CFA0-408A-B511-BA4D71F19068}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -652,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP362"/>
+  <dimension ref="A1:AP365"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38220,7 +38220,7 @@
         <v>31</v>
       </c>
       <c r="L360">
-        <f t="shared" ref="L360:L362" si="7">SUM(O360:V360)</f>
+        <f t="shared" ref="L360" si="7">SUM(O360:V360)</f>
         <v>30</v>
       </c>
       <c r="M360">
@@ -38500,6 +38500,87 @@
       </c>
       <c r="AH362">
         <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A363">
+        <v>2026</v>
+      </c>
+      <c r="B363" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C363">
+        <v>24</v>
+      </c>
+      <c r="D363" t="s">
+        <v>76</v>
+      </c>
+      <c r="E363" t="str">
+        <f>VLOOKUP(D363,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F363" t="s">
+        <v>13</v>
+      </c>
+      <c r="J363" t="s">
+        <v>36</v>
+      </c>
+      <c r="K363" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="364" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A364">
+        <v>2026</v>
+      </c>
+      <c r="B364" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C364">
+        <v>24</v>
+      </c>
+      <c r="D364" t="s">
+        <v>76</v>
+      </c>
+      <c r="E364" t="str">
+        <f>VLOOKUP(D364,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F364" t="s">
+        <v>12</v>
+      </c>
+      <c r="J364" t="s">
+        <v>32</v>
+      </c>
+      <c r="K364" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="365" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A365">
+        <v>2026</v>
+      </c>
+      <c r="B365" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C365">
+        <v>24</v>
+      </c>
+      <c r="D365" t="s">
+        <v>76</v>
+      </c>
+      <c r="E365" t="str">
+        <f>VLOOKUP(D365,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F365" t="s">
+        <v>11</v>
+      </c>
+      <c r="J365" t="s">
+        <v>37</v>
+      </c>
+      <c r="K365" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BB34D29-CFA0-408A-B511-BA4D71F19068}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB5AD76-AE0B-43D7-9171-555509E263FF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -355,6 +355,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
@@ -652,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP365"/>
+  <dimension ref="A1:AP371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38510,7 +38514,7 @@
         <v>46206</v>
       </c>
       <c r="C363">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D363" t="s">
         <v>76</v>
@@ -38522,11 +38526,90 @@
       <c r="F363" t="s">
         <v>13</v>
       </c>
+      <c r="G363">
+        <v>6</v>
+      </c>
+      <c r="H363">
+        <v>0</v>
+      </c>
+      <c r="I363">
+        <v>2</v>
+      </c>
       <c r="J363" t="s">
         <v>36</v>
       </c>
       <c r="K363" t="s">
         <v>31</v>
+      </c>
+      <c r="L363">
+        <f t="shared" ref="L363" si="8">SUM(O363:V363)</f>
+        <v>31</v>
+      </c>
+      <c r="M363">
+        <v>6</v>
+      </c>
+      <c r="N363">
+        <v>5</v>
+      </c>
+      <c r="O363">
+        <v>4</v>
+      </c>
+      <c r="P363">
+        <v>10</v>
+      </c>
+      <c r="Q363">
+        <v>4</v>
+      </c>
+      <c r="R363">
+        <v>7</v>
+      </c>
+      <c r="S363">
+        <v>4</v>
+      </c>
+      <c r="T363">
+        <v>2</v>
+      </c>
+      <c r="U363">
+        <v>0</v>
+      </c>
+      <c r="V363">
+        <v>0</v>
+      </c>
+      <c r="W363">
+        <v>0</v>
+      </c>
+      <c r="X363">
+        <v>0</v>
+      </c>
+      <c r="Y363">
+        <v>0</v>
+      </c>
+      <c r="Z363">
+        <v>0</v>
+      </c>
+      <c r="AA363">
+        <v>0</v>
+      </c>
+      <c r="AB363">
+        <v>0</v>
+      </c>
+      <c r="AC363">
+        <v>0</v>
+      </c>
+      <c r="AD363">
+        <v>0</v>
+      </c>
+      <c r="AE363">
+        <v>0</v>
+      </c>
+      <c r="AF363">
+        <v>0</v>
+      </c>
+      <c r="AG363">
+        <v>0</v>
+      </c>
+      <c r="AH363">
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:34" x14ac:dyDescent="0.35">
@@ -38537,7 +38620,7 @@
         <v>46206</v>
       </c>
       <c r="C364">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D364" t="s">
         <v>76</v>
@@ -38549,11 +38632,90 @@
       <c r="F364" t="s">
         <v>12</v>
       </c>
+      <c r="G364">
+        <v>6</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>3</v>
+      </c>
       <c r="J364" t="s">
         <v>32</v>
       </c>
       <c r="K364" t="s">
         <v>31</v>
+      </c>
+      <c r="L364">
+        <f>SUM(O364:V364)</f>
+        <v>31</v>
+      </c>
+      <c r="M364">
+        <v>4</v>
+      </c>
+      <c r="N364">
+        <v>5</v>
+      </c>
+      <c r="O364">
+        <v>2</v>
+      </c>
+      <c r="P364">
+        <v>15</v>
+      </c>
+      <c r="Q364">
+        <v>3</v>
+      </c>
+      <c r="R364">
+        <v>3</v>
+      </c>
+      <c r="S364">
+        <v>3</v>
+      </c>
+      <c r="T364">
+        <v>2</v>
+      </c>
+      <c r="U364">
+        <v>3</v>
+      </c>
+      <c r="V364">
+        <v>0</v>
+      </c>
+      <c r="W364">
+        <v>0</v>
+      </c>
+      <c r="X364">
+        <v>0</v>
+      </c>
+      <c r="Y364">
+        <v>0</v>
+      </c>
+      <c r="Z364">
+        <v>0</v>
+      </c>
+      <c r="AA364">
+        <v>0</v>
+      </c>
+      <c r="AB364">
+        <v>0</v>
+      </c>
+      <c r="AC364">
+        <v>0</v>
+      </c>
+      <c r="AD364">
+        <v>1</v>
+      </c>
+      <c r="AE364">
+        <v>0</v>
+      </c>
+      <c r="AF364">
+        <v>0</v>
+      </c>
+      <c r="AG364">
+        <v>0</v>
+      </c>
+      <c r="AH364">
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:34" x14ac:dyDescent="0.35">
@@ -38564,7 +38726,7 @@
         <v>46206</v>
       </c>
       <c r="C365">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D365" t="s">
         <v>76</v>
@@ -38576,11 +38738,471 @@
       <c r="F365" t="s">
         <v>11</v>
       </c>
+      <c r="G365">
+        <v>13</v>
+      </c>
+      <c r="H365">
+        <v>6</v>
+      </c>
+      <c r="I365">
+        <v>1</v>
+      </c>
       <c r="J365" t="s">
         <v>37</v>
       </c>
       <c r="K365" t="s">
         <v>31</v>
+      </c>
+      <c r="L365">
+        <f>SUM(O365:V365)</f>
+        <v>32</v>
+      </c>
+      <c r="M365">
+        <v>6</v>
+      </c>
+      <c r="N365">
+        <v>4</v>
+      </c>
+      <c r="O365">
+        <v>11</v>
+      </c>
+      <c r="P365">
+        <v>5</v>
+      </c>
+      <c r="Q365">
+        <v>0</v>
+      </c>
+      <c r="R365">
+        <v>10</v>
+      </c>
+      <c r="S365">
+        <v>1</v>
+      </c>
+      <c r="T365">
+        <v>4</v>
+      </c>
+      <c r="U365">
+        <v>1</v>
+      </c>
+      <c r="V365">
+        <v>0</v>
+      </c>
+      <c r="W365">
+        <v>0</v>
+      </c>
+      <c r="X365">
+        <v>0</v>
+      </c>
+      <c r="Y365">
+        <v>0</v>
+      </c>
+      <c r="Z365">
+        <v>0</v>
+      </c>
+      <c r="AA365">
+        <v>0</v>
+      </c>
+      <c r="AB365">
+        <v>0</v>
+      </c>
+      <c r="AC365">
+        <v>0</v>
+      </c>
+      <c r="AD365">
+        <v>0</v>
+      </c>
+      <c r="AE365">
+        <v>0</v>
+      </c>
+      <c r="AF365">
+        <v>0</v>
+      </c>
+      <c r="AG365">
+        <v>0</v>
+      </c>
+      <c r="AH365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A366">
+        <v>2026</v>
+      </c>
+      <c r="B366" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C366">
+        <v>2</v>
+      </c>
+      <c r="D366" t="s">
+        <v>76</v>
+      </c>
+      <c r="E366" t="str">
+        <f>VLOOKUP(D366,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F366" t="s">
+        <v>11</v>
+      </c>
+      <c r="G366">
+        <v>9</v>
+      </c>
+      <c r="H366">
+        <v>2</v>
+      </c>
+      <c r="I366">
+        <v>2</v>
+      </c>
+      <c r="J366" t="s">
+        <v>36</v>
+      </c>
+      <c r="K366" t="s">
+        <v>31</v>
+      </c>
+      <c r="L366">
+        <f t="shared" ref="L366:L368" si="9">SUM(O366:V366)</f>
+        <v>33</v>
+      </c>
+      <c r="M366">
+        <v>6</v>
+      </c>
+      <c r="N366">
+        <v>4</v>
+      </c>
+      <c r="O366">
+        <v>4</v>
+      </c>
+      <c r="P366">
+        <v>14</v>
+      </c>
+      <c r="Q366">
+        <v>7</v>
+      </c>
+      <c r="R366">
+        <v>6</v>
+      </c>
+      <c r="S366">
+        <v>0</v>
+      </c>
+      <c r="T366">
+        <v>0</v>
+      </c>
+      <c r="U366">
+        <v>0</v>
+      </c>
+      <c r="V366">
+        <v>2</v>
+      </c>
+      <c r="W366">
+        <v>0</v>
+      </c>
+      <c r="X366">
+        <v>0</v>
+      </c>
+      <c r="Y366">
+        <v>0</v>
+      </c>
+      <c r="Z366">
+        <v>0</v>
+      </c>
+      <c r="AA366">
+        <v>0</v>
+      </c>
+      <c r="AB366">
+        <v>0</v>
+      </c>
+      <c r="AC366">
+        <v>0</v>
+      </c>
+      <c r="AD366">
+        <v>0</v>
+      </c>
+      <c r="AE366">
+        <v>0</v>
+      </c>
+      <c r="AF366">
+        <v>0</v>
+      </c>
+      <c r="AG366">
+        <v>0</v>
+      </c>
+      <c r="AH366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A367">
+        <v>2026</v>
+      </c>
+      <c r="B367" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C367">
+        <v>2</v>
+      </c>
+      <c r="D367" t="s">
+        <v>76</v>
+      </c>
+      <c r="E367" t="str">
+        <f>VLOOKUP(D367,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F367" t="s">
+        <v>12</v>
+      </c>
+      <c r="G367">
+        <v>14</v>
+      </c>
+      <c r="H367">
+        <v>6</v>
+      </c>
+      <c r="I367">
+        <v>1</v>
+      </c>
+      <c r="J367" t="s">
+        <v>32</v>
+      </c>
+      <c r="K367" t="s">
+        <v>31</v>
+      </c>
+      <c r="L367">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M367">
+        <v>6</v>
+      </c>
+      <c r="N367">
+        <v>5</v>
+      </c>
+      <c r="O367">
+        <v>2</v>
+      </c>
+      <c r="P367">
+        <v>5</v>
+      </c>
+      <c r="Q367">
+        <v>4</v>
+      </c>
+      <c r="R367">
+        <v>9</v>
+      </c>
+      <c r="S367">
+        <v>4</v>
+      </c>
+      <c r="T367">
+        <v>2</v>
+      </c>
+      <c r="U367">
+        <v>0</v>
+      </c>
+      <c r="V367">
+        <v>4</v>
+      </c>
+      <c r="W367">
+        <v>0</v>
+      </c>
+      <c r="X367">
+        <v>0</v>
+      </c>
+      <c r="Y367">
+        <v>0</v>
+      </c>
+      <c r="Z367">
+        <v>0</v>
+      </c>
+      <c r="AA367">
+        <v>0</v>
+      </c>
+      <c r="AB367">
+        <v>0</v>
+      </c>
+      <c r="AC367">
+        <v>0</v>
+      </c>
+      <c r="AD367">
+        <v>0</v>
+      </c>
+      <c r="AE367">
+        <v>1</v>
+      </c>
+      <c r="AF367">
+        <v>0</v>
+      </c>
+      <c r="AG367">
+        <v>0</v>
+      </c>
+      <c r="AH367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A368">
+        <v>2026</v>
+      </c>
+      <c r="B368" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C368">
+        <v>2</v>
+      </c>
+      <c r="D368" t="s">
+        <v>76</v>
+      </c>
+      <c r="E368" t="str">
+        <f>VLOOKUP(D368,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F368" t="s">
+        <v>13</v>
+      </c>
+      <c r="G368">
+        <v>6</v>
+      </c>
+      <c r="H368">
+        <v>1</v>
+      </c>
+      <c r="I368">
+        <v>3</v>
+      </c>
+      <c r="J368" t="s">
+        <v>37</v>
+      </c>
+      <c r="K368" t="s">
+        <v>31</v>
+      </c>
+      <c r="L368">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M368">
+        <v>6</v>
+      </c>
+      <c r="N368">
+        <v>4</v>
+      </c>
+      <c r="O368">
+        <v>9</v>
+      </c>
+      <c r="P368">
+        <v>0</v>
+      </c>
+      <c r="Q368">
+        <v>4</v>
+      </c>
+      <c r="R368">
+        <v>5</v>
+      </c>
+      <c r="S368">
+        <v>5</v>
+      </c>
+      <c r="T368">
+        <v>5</v>
+      </c>
+      <c r="U368">
+        <v>2</v>
+      </c>
+      <c r="V368">
+        <v>4</v>
+      </c>
+      <c r="W368">
+        <v>0</v>
+      </c>
+      <c r="X368">
+        <v>0</v>
+      </c>
+      <c r="Y368">
+        <v>0</v>
+      </c>
+      <c r="Z368">
+        <v>0</v>
+      </c>
+      <c r="AA368">
+        <v>0</v>
+      </c>
+      <c r="AB368">
+        <v>0</v>
+      </c>
+      <c r="AC368">
+        <v>0</v>
+      </c>
+      <c r="AD368">
+        <v>0</v>
+      </c>
+      <c r="AE368">
+        <v>0</v>
+      </c>
+      <c r="AF368">
+        <v>1</v>
+      </c>
+      <c r="AG368">
+        <v>0</v>
+      </c>
+      <c r="AH368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A369">
+        <v>2026</v>
+      </c>
+      <c r="B369" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C369">
+        <v>3</v>
+      </c>
+      <c r="D369" t="s">
+        <v>76</v>
+      </c>
+      <c r="E369" t="str">
+        <f>VLOOKUP(D369,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="J369" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A370">
+        <v>2026</v>
+      </c>
+      <c r="B370" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C370">
+        <v>3</v>
+      </c>
+      <c r="D370" t="s">
+        <v>76</v>
+      </c>
+      <c r="E370" t="str">
+        <f>VLOOKUP(D370,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="J370" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A371">
+        <v>2026</v>
+      </c>
+      <c r="B371" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C371">
+        <v>3</v>
+      </c>
+      <c r="D371" t="s">
+        <v>76</v>
+      </c>
+      <c r="E371" t="str">
+        <f>VLOOKUP(D371,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="J371" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB5AD76-AE0B-43D7-9171-555509E263FF}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD54C071-A35B-44AC-956C-BA86BF8CD3E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L368" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L371" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -39142,7 +39142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>2026</v>
       </c>
@@ -39159,11 +39159,96 @@
         <f>VLOOKUP(D369,Sheet2!$I$1:$J$12,2,FALSE)</f>
         <v>53.5953349871887, 9.982308366971944</v>
       </c>
+      <c r="F369" t="s">
+        <v>12</v>
+      </c>
+      <c r="G369">
+        <v>7</v>
+      </c>
+      <c r="H369">
+        <v>0</v>
+      </c>
+      <c r="I369">
+        <v>3</v>
+      </c>
       <c r="J369" t="s">
         <v>36</v>
       </c>
+      <c r="K369" t="s">
+        <v>31</v>
+      </c>
+      <c r="L369">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M369">
+        <v>5</v>
+      </c>
+      <c r="N369">
+        <v>4</v>
+      </c>
+      <c r="O369">
+        <v>5</v>
+      </c>
+      <c r="P369">
+        <v>16</v>
+      </c>
+      <c r="Q369">
+        <v>4</v>
+      </c>
+      <c r="R369">
+        <v>8</v>
+      </c>
+      <c r="S369">
+        <v>0</v>
+      </c>
+      <c r="T369">
+        <v>0</v>
+      </c>
+      <c r="U369">
+        <v>0</v>
+      </c>
+      <c r="V369">
+        <v>0</v>
+      </c>
+      <c r="W369">
+        <v>0</v>
+      </c>
+      <c r="X369">
+        <v>0</v>
+      </c>
+      <c r="Y369">
+        <v>0</v>
+      </c>
+      <c r="Z369">
+        <v>0</v>
+      </c>
+      <c r="AA369">
+        <v>0</v>
+      </c>
+      <c r="AB369">
+        <v>0</v>
+      </c>
+      <c r="AC369">
+        <v>0</v>
+      </c>
+      <c r="AD369">
+        <v>0</v>
+      </c>
+      <c r="AE369">
+        <v>0</v>
+      </c>
+      <c r="AF369">
+        <v>0</v>
+      </c>
+      <c r="AG369">
+        <v>0</v>
+      </c>
+      <c r="AH369">
+        <v>0</v>
+      </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>2026</v>
       </c>
@@ -39180,11 +39265,96 @@
         <f>VLOOKUP(D370,Sheet2!$I$1:$J$12,2,FALSE)</f>
         <v>53.5953349871887, 9.982308366971944</v>
       </c>
+      <c r="F370" t="s">
+        <v>13</v>
+      </c>
+      <c r="G370">
+        <v>8</v>
+      </c>
+      <c r="H370">
+        <v>3</v>
+      </c>
+      <c r="I370">
+        <v>2</v>
+      </c>
       <c r="J370" t="s">
         <v>32</v>
       </c>
+      <c r="K370" t="s">
+        <v>31</v>
+      </c>
+      <c r="L370">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M370">
+        <v>6</v>
+      </c>
+      <c r="N370">
+        <v>4</v>
+      </c>
+      <c r="O370">
+        <v>2</v>
+      </c>
+      <c r="P370">
+        <v>0</v>
+      </c>
+      <c r="Q370">
+        <v>9</v>
+      </c>
+      <c r="R370">
+        <v>8</v>
+      </c>
+      <c r="S370">
+        <v>3</v>
+      </c>
+      <c r="T370">
+        <v>2</v>
+      </c>
+      <c r="U370">
+        <v>0</v>
+      </c>
+      <c r="V370">
+        <v>9</v>
+      </c>
+      <c r="W370">
+        <v>0</v>
+      </c>
+      <c r="X370">
+        <v>0</v>
+      </c>
+      <c r="Y370">
+        <v>0</v>
+      </c>
+      <c r="Z370">
+        <v>0</v>
+      </c>
+      <c r="AA370">
+        <v>0</v>
+      </c>
+      <c r="AB370">
+        <v>0</v>
+      </c>
+      <c r="AC370">
+        <v>0</v>
+      </c>
+      <c r="AD370">
+        <v>0</v>
+      </c>
+      <c r="AE370">
+        <v>0</v>
+      </c>
+      <c r="AF370">
+        <v>0</v>
+      </c>
+      <c r="AG370">
+        <v>0</v>
+      </c>
+      <c r="AH370">
+        <v>0</v>
+      </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>2026</v>
       </c>
@@ -39201,8 +39371,93 @@
         <f>VLOOKUP(D371,Sheet2!$I$1:$J$12,2,FALSE)</f>
         <v>53.5953349871887, 9.982308366971944</v>
       </c>
+      <c r="F371" t="s">
+        <v>11</v>
+      </c>
+      <c r="G371">
+        <v>13</v>
+      </c>
+      <c r="H371">
+        <v>6</v>
+      </c>
+      <c r="I371">
+        <v>1</v>
+      </c>
       <c r="J371" t="s">
         <v>37</v>
+      </c>
+      <c r="K371" t="s">
+        <v>31</v>
+      </c>
+      <c r="L371">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M371">
+        <v>5</v>
+      </c>
+      <c r="N371">
+        <v>3</v>
+      </c>
+      <c r="O371">
+        <v>0</v>
+      </c>
+      <c r="P371">
+        <v>12</v>
+      </c>
+      <c r="Q371">
+        <v>8</v>
+      </c>
+      <c r="R371">
+        <v>5</v>
+      </c>
+      <c r="S371">
+        <v>0</v>
+      </c>
+      <c r="T371">
+        <v>0</v>
+      </c>
+      <c r="U371">
+        <v>0</v>
+      </c>
+      <c r="V371">
+        <v>8</v>
+      </c>
+      <c r="W371">
+        <v>0</v>
+      </c>
+      <c r="X371">
+        <v>0</v>
+      </c>
+      <c r="Y371">
+        <v>1</v>
+      </c>
+      <c r="Z371">
+        <v>0</v>
+      </c>
+      <c r="AA371">
+        <v>0</v>
+      </c>
+      <c r="AB371">
+        <v>0</v>
+      </c>
+      <c r="AC371">
+        <v>0</v>
+      </c>
+      <c r="AD371">
+        <v>1</v>
+      </c>
+      <c r="AE371">
+        <v>0</v>
+      </c>
+      <c r="AF371">
+        <v>0</v>
+      </c>
+      <c r="AG371">
+        <v>0</v>
+      </c>
+      <c r="AH371">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD54C071-A35B-44AC-956C-BA86BF8CD3E3}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4518A147-A799-4392-B21A-F7A274D5470B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP371"/>
+  <dimension ref="A1:AP374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L371" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L374" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -39458,6 +39458,324 @@
       </c>
       <c r="AH371">
         <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A372">
+        <v>2026</v>
+      </c>
+      <c r="B372" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C372">
+        <v>4</v>
+      </c>
+      <c r="D372" t="s">
+        <v>76</v>
+      </c>
+      <c r="E372" t="str">
+        <f>VLOOKUP(D372,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F372" t="s">
+        <v>11</v>
+      </c>
+      <c r="G372">
+        <v>10</v>
+      </c>
+      <c r="H372">
+        <v>2</v>
+      </c>
+      <c r="I372">
+        <v>2</v>
+      </c>
+      <c r="J372" t="s">
+        <v>36</v>
+      </c>
+      <c r="K372" t="s">
+        <v>31</v>
+      </c>
+      <c r="L372">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M372">
+        <v>5</v>
+      </c>
+      <c r="N372">
+        <v>5</v>
+      </c>
+      <c r="O372">
+        <v>2</v>
+      </c>
+      <c r="P372">
+        <v>10</v>
+      </c>
+      <c r="Q372">
+        <v>5</v>
+      </c>
+      <c r="R372">
+        <v>5</v>
+      </c>
+      <c r="S372">
+        <v>2</v>
+      </c>
+      <c r="T372">
+        <v>2</v>
+      </c>
+      <c r="U372">
+        <v>0</v>
+      </c>
+      <c r="V372">
+        <v>5</v>
+      </c>
+      <c r="W372">
+        <v>0</v>
+      </c>
+      <c r="X372">
+        <v>0</v>
+      </c>
+      <c r="Y372">
+        <v>0</v>
+      </c>
+      <c r="Z372">
+        <v>0</v>
+      </c>
+      <c r="AA372">
+        <v>0</v>
+      </c>
+      <c r="AB372">
+        <v>0</v>
+      </c>
+      <c r="AC372">
+        <v>1</v>
+      </c>
+      <c r="AD372">
+        <v>0</v>
+      </c>
+      <c r="AE372">
+        <v>0</v>
+      </c>
+      <c r="AF372">
+        <v>0</v>
+      </c>
+      <c r="AG372">
+        <v>0</v>
+      </c>
+      <c r="AH372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A373">
+        <v>2026</v>
+      </c>
+      <c r="B373" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C373">
+        <v>4</v>
+      </c>
+      <c r="D373" t="s">
+        <v>76</v>
+      </c>
+      <c r="E373" t="str">
+        <f>VLOOKUP(D373,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F373" t="s">
+        <v>13</v>
+      </c>
+      <c r="G373">
+        <v>13</v>
+      </c>
+      <c r="H373">
+        <v>6</v>
+      </c>
+      <c r="I373">
+        <v>1</v>
+      </c>
+      <c r="J373" t="s">
+        <v>32</v>
+      </c>
+      <c r="K373" t="s">
+        <v>31</v>
+      </c>
+      <c r="L373">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M373">
+        <v>5</v>
+      </c>
+      <c r="N373">
+        <v>5</v>
+      </c>
+      <c r="O373">
+        <v>2</v>
+      </c>
+      <c r="P373">
+        <v>4</v>
+      </c>
+      <c r="Q373">
+        <v>9</v>
+      </c>
+      <c r="R373">
+        <v>6</v>
+      </c>
+      <c r="S373">
+        <v>3</v>
+      </c>
+      <c r="T373">
+        <v>2</v>
+      </c>
+      <c r="U373">
+        <v>4</v>
+      </c>
+      <c r="V373">
+        <v>0</v>
+      </c>
+      <c r="W373">
+        <v>0</v>
+      </c>
+      <c r="X373">
+        <v>0</v>
+      </c>
+      <c r="Y373">
+        <v>0</v>
+      </c>
+      <c r="Z373">
+        <v>0</v>
+      </c>
+      <c r="AA373">
+        <v>0</v>
+      </c>
+      <c r="AB373">
+        <v>0</v>
+      </c>
+      <c r="AC373">
+        <v>0</v>
+      </c>
+      <c r="AD373">
+        <v>0</v>
+      </c>
+      <c r="AE373">
+        <v>0</v>
+      </c>
+      <c r="AF373">
+        <v>0</v>
+      </c>
+      <c r="AG373">
+        <v>0</v>
+      </c>
+      <c r="AH373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A374">
+        <v>2026</v>
+      </c>
+      <c r="B374" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C374">
+        <v>4</v>
+      </c>
+      <c r="D374" t="s">
+        <v>76</v>
+      </c>
+      <c r="E374" t="str">
+        <f>VLOOKUP(D374,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F374" t="s">
+        <v>12</v>
+      </c>
+      <c r="G374">
+        <v>8</v>
+      </c>
+      <c r="H374">
+        <v>2</v>
+      </c>
+      <c r="I374">
+        <v>3</v>
+      </c>
+      <c r="J374" t="s">
+        <v>37</v>
+      </c>
+      <c r="K374" t="s">
+        <v>31</v>
+      </c>
+      <c r="L374">
+        <f t="shared" si="9"/>
+        <v>37</v>
+      </c>
+      <c r="M374">
+        <v>6</v>
+      </c>
+      <c r="N374">
+        <v>4</v>
+      </c>
+      <c r="O374">
+        <v>5</v>
+      </c>
+      <c r="P374">
+        <v>0</v>
+      </c>
+      <c r="Q374">
+        <v>12</v>
+      </c>
+      <c r="R374">
+        <v>3</v>
+      </c>
+      <c r="S374">
+        <v>4</v>
+      </c>
+      <c r="T374">
+        <v>0</v>
+      </c>
+      <c r="U374">
+        <v>4</v>
+      </c>
+      <c r="V374">
+        <v>9</v>
+      </c>
+      <c r="W374">
+        <v>0</v>
+      </c>
+      <c r="X374">
+        <v>0</v>
+      </c>
+      <c r="Y374">
+        <v>0</v>
+      </c>
+      <c r="Z374">
+        <v>0</v>
+      </c>
+      <c r="AA374">
+        <v>0</v>
+      </c>
+      <c r="AB374">
+        <v>0</v>
+      </c>
+      <c r="AC374">
+        <v>0</v>
+      </c>
+      <c r="AD374">
+        <v>0</v>
+      </c>
+      <c r="AE374">
+        <v>0</v>
+      </c>
+      <c r="AF374">
+        <v>0</v>
+      </c>
+      <c r="AG374">
+        <v>0</v>
+      </c>
+      <c r="AH374">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4518A147-A799-4392-B21A-F7A274D5470B}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63A3006-B771-4794-A5CC-6DBBDF635E1F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$377</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP374"/>
+  <dimension ref="A1:AP377"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L374" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L377" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -39778,8 +39778,326 @@
         <v>1</v>
       </c>
     </row>
+    <row r="375" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A375">
+        <v>2026</v>
+      </c>
+      <c r="B375" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C375">
+        <v>5</v>
+      </c>
+      <c r="D375" t="s">
+        <v>76</v>
+      </c>
+      <c r="E375" t="str">
+        <f>VLOOKUP(D375,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F375" t="s">
+        <v>11</v>
+      </c>
+      <c r="G375">
+        <v>10</v>
+      </c>
+      <c r="H375">
+        <v>4</v>
+      </c>
+      <c r="I375">
+        <v>2</v>
+      </c>
+      <c r="J375" t="s">
+        <v>36</v>
+      </c>
+      <c r="K375" t="s">
+        <v>31</v>
+      </c>
+      <c r="L375">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M375">
+        <v>5</v>
+      </c>
+      <c r="N375">
+        <v>4</v>
+      </c>
+      <c r="O375">
+        <v>5</v>
+      </c>
+      <c r="P375">
+        <v>3</v>
+      </c>
+      <c r="Q375">
+        <v>7</v>
+      </c>
+      <c r="R375">
+        <v>12</v>
+      </c>
+      <c r="S375">
+        <v>0</v>
+      </c>
+      <c r="T375">
+        <v>0</v>
+      </c>
+      <c r="U375">
+        <v>0</v>
+      </c>
+      <c r="V375">
+        <v>7</v>
+      </c>
+      <c r="W375">
+        <v>0</v>
+      </c>
+      <c r="X375">
+        <v>0</v>
+      </c>
+      <c r="Y375">
+        <v>0</v>
+      </c>
+      <c r="Z375">
+        <v>0</v>
+      </c>
+      <c r="AA375">
+        <v>0</v>
+      </c>
+      <c r="AB375">
+        <v>0</v>
+      </c>
+      <c r="AC375">
+        <v>0</v>
+      </c>
+      <c r="AD375">
+        <v>1</v>
+      </c>
+      <c r="AE375">
+        <v>0</v>
+      </c>
+      <c r="AF375">
+        <v>0</v>
+      </c>
+      <c r="AG375">
+        <v>0</v>
+      </c>
+      <c r="AH375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A376">
+        <v>2026</v>
+      </c>
+      <c r="B376" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C376">
+        <v>5</v>
+      </c>
+      <c r="D376" t="s">
+        <v>76</v>
+      </c>
+      <c r="E376" t="str">
+        <f>VLOOKUP(D376,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F376" t="s">
+        <v>12</v>
+      </c>
+      <c r="G376">
+        <v>13</v>
+      </c>
+      <c r="H376">
+        <v>7</v>
+      </c>
+      <c r="I376">
+        <v>1</v>
+      </c>
+      <c r="J376" t="s">
+        <v>32</v>
+      </c>
+      <c r="K376" t="s">
+        <v>31</v>
+      </c>
+      <c r="L376">
+        <f t="shared" si="9"/>
+        <v>32</v>
+      </c>
+      <c r="M376">
+        <v>6</v>
+      </c>
+      <c r="N376">
+        <v>5</v>
+      </c>
+      <c r="O376">
+        <v>1</v>
+      </c>
+      <c r="P376">
+        <v>3</v>
+      </c>
+      <c r="Q376">
+        <v>5</v>
+      </c>
+      <c r="R376">
+        <v>12</v>
+      </c>
+      <c r="S376">
+        <v>5</v>
+      </c>
+      <c r="T376">
+        <v>1</v>
+      </c>
+      <c r="U376">
+        <v>0</v>
+      </c>
+      <c r="V376">
+        <v>5</v>
+      </c>
+      <c r="W376">
+        <v>0</v>
+      </c>
+      <c r="X376">
+        <v>0</v>
+      </c>
+      <c r="Y376">
+        <v>0</v>
+      </c>
+      <c r="Z376">
+        <v>0</v>
+      </c>
+      <c r="AA376">
+        <v>0</v>
+      </c>
+      <c r="AB376">
+        <v>0</v>
+      </c>
+      <c r="AC376">
+        <v>0</v>
+      </c>
+      <c r="AD376">
+        <v>0</v>
+      </c>
+      <c r="AE376">
+        <v>0</v>
+      </c>
+      <c r="AF376">
+        <v>1</v>
+      </c>
+      <c r="AG376">
+        <v>0</v>
+      </c>
+      <c r="AH376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A377">
+        <v>2026</v>
+      </c>
+      <c r="B377" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C377">
+        <v>5</v>
+      </c>
+      <c r="D377" t="s">
+        <v>76</v>
+      </c>
+      <c r="E377" t="str">
+        <f>VLOOKUP(D377,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F377" t="s">
+        <v>13</v>
+      </c>
+      <c r="G377">
+        <v>6</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>3</v>
+      </c>
+      <c r="J377" t="s">
+        <v>37</v>
+      </c>
+      <c r="K377" t="s">
+        <v>31</v>
+      </c>
+      <c r="L377">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M377">
+        <v>5</v>
+      </c>
+      <c r="N377">
+        <v>4</v>
+      </c>
+      <c r="O377">
+        <v>4</v>
+      </c>
+      <c r="P377">
+        <v>0</v>
+      </c>
+      <c r="Q377">
+        <v>2</v>
+      </c>
+      <c r="R377">
+        <v>9</v>
+      </c>
+      <c r="S377">
+        <v>10</v>
+      </c>
+      <c r="T377">
+        <v>4</v>
+      </c>
+      <c r="U377">
+        <v>5</v>
+      </c>
+      <c r="V377">
+        <v>0</v>
+      </c>
+      <c r="W377">
+        <v>0</v>
+      </c>
+      <c r="X377">
+        <v>0</v>
+      </c>
+      <c r="Y377">
+        <v>0</v>
+      </c>
+      <c r="Z377">
+        <v>0</v>
+      </c>
+      <c r="AA377">
+        <v>0</v>
+      </c>
+      <c r="AB377">
+        <v>0</v>
+      </c>
+      <c r="AC377">
+        <v>0</v>
+      </c>
+      <c r="AD377">
+        <v>0</v>
+      </c>
+      <c r="AE377">
+        <v>0</v>
+      </c>
+      <c r="AF377">
+        <v>0</v>
+      </c>
+      <c r="AG377">
+        <v>0</v>
+      </c>
+      <c r="AH377">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP350" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
+  <autoFilter ref="A2:AP377" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
   <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63A3006-B771-4794-A5CC-6DBBDF635E1F}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36FE8875-7D3E-46CF-BDEF-F96468EAABCC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP377"/>
+  <dimension ref="A1:AP380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L377" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L380" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -40093,6 +40093,324 @@
         <v>0</v>
       </c>
       <c r="AH377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A378">
+        <v>2026</v>
+      </c>
+      <c r="B378" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C378">
+        <v>6</v>
+      </c>
+      <c r="D378" t="s">
+        <v>76</v>
+      </c>
+      <c r="E378" t="str">
+        <f>VLOOKUP(D378,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F378" t="s">
+        <v>13</v>
+      </c>
+      <c r="G378">
+        <v>12</v>
+      </c>
+      <c r="H378">
+        <v>4</v>
+      </c>
+      <c r="I378">
+        <v>2</v>
+      </c>
+      <c r="J378" t="s">
+        <v>36</v>
+      </c>
+      <c r="K378" t="s">
+        <v>31</v>
+      </c>
+      <c r="L378">
+        <f t="shared" si="9"/>
+        <v>29</v>
+      </c>
+      <c r="M378">
+        <v>6</v>
+      </c>
+      <c r="N378">
+        <v>4</v>
+      </c>
+      <c r="O378">
+        <v>5</v>
+      </c>
+      <c r="P378">
+        <v>14</v>
+      </c>
+      <c r="Q378">
+        <v>5</v>
+      </c>
+      <c r="R378">
+        <v>0</v>
+      </c>
+      <c r="S378">
+        <v>3</v>
+      </c>
+      <c r="T378">
+        <v>0</v>
+      </c>
+      <c r="U378">
+        <v>0</v>
+      </c>
+      <c r="V378">
+        <v>2</v>
+      </c>
+      <c r="W378">
+        <v>0</v>
+      </c>
+      <c r="X378">
+        <v>0</v>
+      </c>
+      <c r="Y378">
+        <v>0</v>
+      </c>
+      <c r="Z378">
+        <v>0</v>
+      </c>
+      <c r="AA378">
+        <v>0</v>
+      </c>
+      <c r="AB378">
+        <v>0</v>
+      </c>
+      <c r="AC378">
+        <v>1</v>
+      </c>
+      <c r="AD378">
+        <v>1</v>
+      </c>
+      <c r="AE378">
+        <v>0</v>
+      </c>
+      <c r="AF378">
+        <v>0</v>
+      </c>
+      <c r="AG378">
+        <v>0</v>
+      </c>
+      <c r="AH378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A379">
+        <v>2026</v>
+      </c>
+      <c r="B379" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C379">
+        <v>6</v>
+      </c>
+      <c r="D379" t="s">
+        <v>76</v>
+      </c>
+      <c r="E379" t="str">
+        <f>VLOOKUP(D379,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F379" t="s">
+        <v>12</v>
+      </c>
+      <c r="G379">
+        <v>11</v>
+      </c>
+      <c r="H379">
+        <v>3</v>
+      </c>
+      <c r="I379">
+        <v>3</v>
+      </c>
+      <c r="J379" t="s">
+        <v>32</v>
+      </c>
+      <c r="K379" t="s">
+        <v>31</v>
+      </c>
+      <c r="L379">
+        <f t="shared" si="9"/>
+        <v>37</v>
+      </c>
+      <c r="M379">
+        <v>4</v>
+      </c>
+      <c r="N379">
+        <v>4</v>
+      </c>
+      <c r="O379">
+        <v>8</v>
+      </c>
+      <c r="P379">
+        <v>5</v>
+      </c>
+      <c r="Q379">
+        <v>0</v>
+      </c>
+      <c r="R379">
+        <v>16</v>
+      </c>
+      <c r="S379">
+        <v>4</v>
+      </c>
+      <c r="T379">
+        <v>4</v>
+      </c>
+      <c r="U379">
+        <v>0</v>
+      </c>
+      <c r="V379">
+        <v>0</v>
+      </c>
+      <c r="W379">
+        <v>0</v>
+      </c>
+      <c r="X379">
+        <v>0</v>
+      </c>
+      <c r="Y379">
+        <v>0</v>
+      </c>
+      <c r="Z379">
+        <v>0</v>
+      </c>
+      <c r="AA379">
+        <v>0</v>
+      </c>
+      <c r="AB379">
+        <v>0</v>
+      </c>
+      <c r="AC379">
+        <v>0</v>
+      </c>
+      <c r="AD379">
+        <v>0</v>
+      </c>
+      <c r="AE379">
+        <v>0</v>
+      </c>
+      <c r="AF379">
+        <v>0</v>
+      </c>
+      <c r="AG379">
+        <v>0</v>
+      </c>
+      <c r="AH379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A380">
+        <v>2026</v>
+      </c>
+      <c r="B380" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C380">
+        <v>6</v>
+      </c>
+      <c r="D380" t="s">
+        <v>76</v>
+      </c>
+      <c r="E380" t="str">
+        <f>VLOOKUP(D380,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F380" t="s">
+        <v>11</v>
+      </c>
+      <c r="G380">
+        <v>13</v>
+      </c>
+      <c r="H380">
+        <v>3</v>
+      </c>
+      <c r="I380">
+        <v>1</v>
+      </c>
+      <c r="J380" t="s">
+        <v>37</v>
+      </c>
+      <c r="K380" t="s">
+        <v>31</v>
+      </c>
+      <c r="L380">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M380">
+        <v>5</v>
+      </c>
+      <c r="N380">
+        <v>4</v>
+      </c>
+      <c r="O380">
+        <v>8</v>
+      </c>
+      <c r="P380">
+        <v>10</v>
+      </c>
+      <c r="Q380">
+        <v>0</v>
+      </c>
+      <c r="R380">
+        <v>10</v>
+      </c>
+      <c r="S380">
+        <v>3</v>
+      </c>
+      <c r="T380">
+        <v>4</v>
+      </c>
+      <c r="U380">
+        <v>0</v>
+      </c>
+      <c r="V380">
+        <v>0</v>
+      </c>
+      <c r="W380">
+        <v>0</v>
+      </c>
+      <c r="X380">
+        <v>0</v>
+      </c>
+      <c r="Y380">
+        <v>0</v>
+      </c>
+      <c r="Z380">
+        <v>0</v>
+      </c>
+      <c r="AA380">
+        <v>0</v>
+      </c>
+      <c r="AB380">
+        <v>0</v>
+      </c>
+      <c r="AC380">
+        <v>0</v>
+      </c>
+      <c r="AD380">
+        <v>0</v>
+      </c>
+      <c r="AE380">
+        <v>1</v>
+      </c>
+      <c r="AF380">
+        <v>1</v>
+      </c>
+      <c r="AG380">
+        <v>0</v>
+      </c>
+      <c r="AH380">
         <v>0</v>
       </c>
     </row>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36FE8875-7D3E-46CF-BDEF-F96468EAABCC}"/>
+  <xr:revisionPtr revIDLastSave="659" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A4DD37-5F6E-4C4E-96C1-6414834A069A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP380"/>
+  <dimension ref="A1:AP383"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L380" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L383" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -40414,9 +40414,327 @@
         <v>0</v>
       </c>
     </row>
+    <row r="381" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A381">
+        <v>2026</v>
+      </c>
+      <c r="B381" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C381">
+        <v>7</v>
+      </c>
+      <c r="D381" t="s">
+        <v>76</v>
+      </c>
+      <c r="E381" t="str">
+        <f>VLOOKUP(D381,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F381" t="s">
+        <v>12</v>
+      </c>
+      <c r="G381">
+        <v>13</v>
+      </c>
+      <c r="H381">
+        <v>5</v>
+      </c>
+      <c r="I381">
+        <v>1</v>
+      </c>
+      <c r="J381" t="s">
+        <v>36</v>
+      </c>
+      <c r="K381" t="s">
+        <v>31</v>
+      </c>
+      <c r="L381">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M381">
+        <v>5</v>
+      </c>
+      <c r="N381">
+        <v>4</v>
+      </c>
+      <c r="O381">
+        <v>4</v>
+      </c>
+      <c r="P381">
+        <v>6</v>
+      </c>
+      <c r="Q381">
+        <v>0</v>
+      </c>
+      <c r="R381">
+        <v>12</v>
+      </c>
+      <c r="S381">
+        <v>7</v>
+      </c>
+      <c r="T381">
+        <v>0</v>
+      </c>
+      <c r="U381">
+        <v>2</v>
+      </c>
+      <c r="V381">
+        <v>0</v>
+      </c>
+      <c r="W381">
+        <v>0</v>
+      </c>
+      <c r="X381">
+        <v>0</v>
+      </c>
+      <c r="Y381">
+        <v>0</v>
+      </c>
+      <c r="Z381">
+        <v>0</v>
+      </c>
+      <c r="AA381">
+        <v>0</v>
+      </c>
+      <c r="AB381">
+        <v>0</v>
+      </c>
+      <c r="AC381">
+        <v>0</v>
+      </c>
+      <c r="AD381">
+        <v>0</v>
+      </c>
+      <c r="AE381">
+        <v>0</v>
+      </c>
+      <c r="AF381">
+        <v>0</v>
+      </c>
+      <c r="AG381">
+        <v>0</v>
+      </c>
+      <c r="AH381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A382">
+        <v>2026</v>
+      </c>
+      <c r="B382" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C382">
+        <v>7</v>
+      </c>
+      <c r="D382" t="s">
+        <v>76</v>
+      </c>
+      <c r="E382" t="str">
+        <f>VLOOKUP(D382,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F382" t="s">
+        <v>11</v>
+      </c>
+      <c r="G382">
+        <v>11</v>
+      </c>
+      <c r="H382">
+        <v>5</v>
+      </c>
+      <c r="I382">
+        <v>2</v>
+      </c>
+      <c r="J382" t="s">
+        <v>32</v>
+      </c>
+      <c r="K382" t="s">
+        <v>31</v>
+      </c>
+      <c r="L382">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M382">
+        <v>6</v>
+      </c>
+      <c r="N382">
+        <v>4</v>
+      </c>
+      <c r="O382">
+        <v>7</v>
+      </c>
+      <c r="P382">
+        <v>8</v>
+      </c>
+      <c r="Q382">
+        <v>4</v>
+      </c>
+      <c r="R382">
+        <v>8</v>
+      </c>
+      <c r="S382">
+        <v>0</v>
+      </c>
+      <c r="T382">
+        <v>7</v>
+      </c>
+      <c r="U382">
+        <v>0</v>
+      </c>
+      <c r="V382">
+        <v>0</v>
+      </c>
+      <c r="W382">
+        <v>0</v>
+      </c>
+      <c r="X382">
+        <v>0</v>
+      </c>
+      <c r="Y382">
+        <v>0</v>
+      </c>
+      <c r="Z382">
+        <v>0</v>
+      </c>
+      <c r="AA382">
+        <v>0</v>
+      </c>
+      <c r="AB382">
+        <v>0</v>
+      </c>
+      <c r="AC382">
+        <v>1</v>
+      </c>
+      <c r="AD382">
+        <v>0</v>
+      </c>
+      <c r="AE382">
+        <v>0</v>
+      </c>
+      <c r="AF382">
+        <v>1</v>
+      </c>
+      <c r="AG382">
+        <v>0</v>
+      </c>
+      <c r="AH382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A383">
+        <v>2026</v>
+      </c>
+      <c r="B383" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C383">
+        <v>7</v>
+      </c>
+      <c r="D383" t="s">
+        <v>76</v>
+      </c>
+      <c r="E383" t="str">
+        <f>VLOOKUP(D383,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F383" t="s">
+        <v>13</v>
+      </c>
+      <c r="G383">
+        <v>6</v>
+      </c>
+      <c r="H383">
+        <v>0</v>
+      </c>
+      <c r="I383">
+        <v>3</v>
+      </c>
+      <c r="J383" t="s">
+        <v>37</v>
+      </c>
+      <c r="K383" t="s">
+        <v>31</v>
+      </c>
+      <c r="L383">
+        <f t="shared" si="9"/>
+        <v>34</v>
+      </c>
+      <c r="M383">
+        <v>5</v>
+      </c>
+      <c r="N383">
+        <v>5</v>
+      </c>
+      <c r="O383">
+        <v>9</v>
+      </c>
+      <c r="P383">
+        <v>5</v>
+      </c>
+      <c r="Q383">
+        <v>3</v>
+      </c>
+      <c r="R383">
+        <v>3</v>
+      </c>
+      <c r="S383">
+        <v>2</v>
+      </c>
+      <c r="T383">
+        <v>9</v>
+      </c>
+      <c r="U383">
+        <v>0</v>
+      </c>
+      <c r="V383">
+        <v>3</v>
+      </c>
+      <c r="W383">
+        <v>0</v>
+      </c>
+      <c r="X383">
+        <v>0</v>
+      </c>
+      <c r="Y383">
+        <v>0</v>
+      </c>
+      <c r="Z383">
+        <v>0</v>
+      </c>
+      <c r="AA383">
+        <v>0</v>
+      </c>
+      <c r="AB383">
+        <v>0</v>
+      </c>
+      <c r="AC383">
+        <v>1</v>
+      </c>
+      <c r="AD383">
+        <v>0</v>
+      </c>
+      <c r="AE383">
+        <v>0</v>
+      </c>
+      <c r="AF383">
+        <v>0</v>
+      </c>
+      <c r="AG383">
+        <v>0</v>
+      </c>
+      <c r="AH383">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:AP377" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>
       <formula2>1</formula2>
@@ -40426,7 +40744,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{761EF6A8-1D47-4E5D-B2B8-225F6EE4B0A2}">
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$3</xm:f>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="659" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A4DD37-5F6E-4C4E-96C1-6414834A069A}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C07282-3C17-4968-8D8D-AB0CA1D5EC3C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AP$389</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP383"/>
+  <dimension ref="A1:AP389"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L383" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L389" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -40732,9 +40732,645 @@
         <v>0</v>
       </c>
     </row>
+    <row r="384" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A384">
+        <v>2026</v>
+      </c>
+      <c r="B384" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C384">
+        <v>8</v>
+      </c>
+      <c r="D384" t="s">
+        <v>76</v>
+      </c>
+      <c r="E384" t="str">
+        <f>VLOOKUP(D384,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F384" t="s">
+        <v>13</v>
+      </c>
+      <c r="G384">
+        <v>6</v>
+      </c>
+      <c r="H384">
+        <v>2</v>
+      </c>
+      <c r="I384">
+        <v>3</v>
+      </c>
+      <c r="J384" t="s">
+        <v>36</v>
+      </c>
+      <c r="K384" t="s">
+        <v>31</v>
+      </c>
+      <c r="L384">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M384">
+        <v>6</v>
+      </c>
+      <c r="N384">
+        <v>5</v>
+      </c>
+      <c r="O384">
+        <v>2</v>
+      </c>
+      <c r="P384">
+        <v>3</v>
+      </c>
+      <c r="Q384">
+        <v>5</v>
+      </c>
+      <c r="R384">
+        <v>4</v>
+      </c>
+      <c r="S384">
+        <v>7</v>
+      </c>
+      <c r="T384">
+        <v>2</v>
+      </c>
+      <c r="U384">
+        <v>7</v>
+      </c>
+      <c r="V384">
+        <v>0</v>
+      </c>
+      <c r="W384">
+        <v>0</v>
+      </c>
+      <c r="X384">
+        <v>0</v>
+      </c>
+      <c r="Y384">
+        <v>0</v>
+      </c>
+      <c r="Z384">
+        <v>0</v>
+      </c>
+      <c r="AA384">
+        <v>0</v>
+      </c>
+      <c r="AB384">
+        <v>0</v>
+      </c>
+      <c r="AC384">
+        <v>0</v>
+      </c>
+      <c r="AD384">
+        <v>0</v>
+      </c>
+      <c r="AE384">
+        <v>1</v>
+      </c>
+      <c r="AF384">
+        <v>0</v>
+      </c>
+      <c r="AG384">
+        <v>0</v>
+      </c>
+      <c r="AH384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A385">
+        <v>2026</v>
+      </c>
+      <c r="B385" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C385">
+        <v>8</v>
+      </c>
+      <c r="D385" t="s">
+        <v>76</v>
+      </c>
+      <c r="E385" t="str">
+        <f>VLOOKUP(D385,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F385" t="s">
+        <v>12</v>
+      </c>
+      <c r="G385">
+        <v>11</v>
+      </c>
+      <c r="H385">
+        <v>5</v>
+      </c>
+      <c r="I385">
+        <v>2</v>
+      </c>
+      <c r="J385" t="s">
+        <v>32</v>
+      </c>
+      <c r="K385" t="s">
+        <v>31</v>
+      </c>
+      <c r="L385">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="M385">
+        <v>5</v>
+      </c>
+      <c r="N385">
+        <v>5</v>
+      </c>
+      <c r="O385">
+        <v>3</v>
+      </c>
+      <c r="P385">
+        <v>4</v>
+      </c>
+      <c r="Q385">
+        <v>7</v>
+      </c>
+      <c r="R385">
+        <v>4</v>
+      </c>
+      <c r="S385">
+        <v>4</v>
+      </c>
+      <c r="T385">
+        <v>0</v>
+      </c>
+      <c r="U385">
+        <v>4</v>
+      </c>
+      <c r="V385">
+        <v>7</v>
+      </c>
+      <c r="W385">
+        <v>0</v>
+      </c>
+      <c r="X385">
+        <v>0</v>
+      </c>
+      <c r="Y385">
+        <v>0</v>
+      </c>
+      <c r="Z385">
+        <v>0</v>
+      </c>
+      <c r="AA385">
+        <v>0</v>
+      </c>
+      <c r="AB385">
+        <v>0</v>
+      </c>
+      <c r="AC385">
+        <v>0</v>
+      </c>
+      <c r="AD385">
+        <v>0</v>
+      </c>
+      <c r="AE385">
+        <v>0</v>
+      </c>
+      <c r="AF385">
+        <v>0</v>
+      </c>
+      <c r="AG385">
+        <v>0</v>
+      </c>
+      <c r="AH385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A386">
+        <v>2026</v>
+      </c>
+      <c r="B386" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C386">
+        <v>8</v>
+      </c>
+      <c r="D386" t="s">
+        <v>76</v>
+      </c>
+      <c r="E386" t="str">
+        <f>VLOOKUP(D386,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F386" t="s">
+        <v>11</v>
+      </c>
+      <c r="G386">
+        <v>14</v>
+      </c>
+      <c r="H386">
+        <v>5</v>
+      </c>
+      <c r="I386">
+        <v>1</v>
+      </c>
+      <c r="J386" t="s">
+        <v>37</v>
+      </c>
+      <c r="K386" t="s">
+        <v>31</v>
+      </c>
+      <c r="L386">
+        <f t="shared" si="9"/>
+        <v>29</v>
+      </c>
+      <c r="M386">
+        <v>6</v>
+      </c>
+      <c r="N386">
+        <v>5</v>
+      </c>
+      <c r="O386">
+        <v>8</v>
+      </c>
+      <c r="P386">
+        <v>4</v>
+      </c>
+      <c r="Q386">
+        <v>2</v>
+      </c>
+      <c r="R386">
+        <v>2</v>
+      </c>
+      <c r="S386">
+        <v>5</v>
+      </c>
+      <c r="T386">
+        <v>8</v>
+      </c>
+      <c r="U386">
+        <v>0</v>
+      </c>
+      <c r="V386">
+        <v>0</v>
+      </c>
+      <c r="W386">
+        <v>0</v>
+      </c>
+      <c r="X386">
+        <v>0</v>
+      </c>
+      <c r="Y386">
+        <v>0</v>
+      </c>
+      <c r="Z386">
+        <v>0</v>
+      </c>
+      <c r="AA386">
+        <v>0</v>
+      </c>
+      <c r="AB386">
+        <v>0</v>
+      </c>
+      <c r="AC386">
+        <v>0</v>
+      </c>
+      <c r="AD386">
+        <v>0</v>
+      </c>
+      <c r="AE386">
+        <v>0</v>
+      </c>
+      <c r="AF386">
+        <v>0</v>
+      </c>
+      <c r="AG386">
+        <v>1</v>
+      </c>
+      <c r="AH386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A387">
+        <v>2026</v>
+      </c>
+      <c r="B387" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C387">
+        <v>9</v>
+      </c>
+      <c r="D387" t="s">
+        <v>76</v>
+      </c>
+      <c r="E387" t="str">
+        <f>VLOOKUP(D387,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F387" t="s">
+        <v>11</v>
+      </c>
+      <c r="G387">
+        <v>13</v>
+      </c>
+      <c r="H387">
+        <v>8</v>
+      </c>
+      <c r="I387">
+        <v>1</v>
+      </c>
+      <c r="J387" t="s">
+        <v>36</v>
+      </c>
+      <c r="K387" t="s">
+        <v>31</v>
+      </c>
+      <c r="L387">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="M387">
+        <v>5</v>
+      </c>
+      <c r="N387">
+        <v>4</v>
+      </c>
+      <c r="O387">
+        <v>3</v>
+      </c>
+      <c r="P387">
+        <v>0</v>
+      </c>
+      <c r="Q387">
+        <v>5</v>
+      </c>
+      <c r="R387">
+        <v>10</v>
+      </c>
+      <c r="S387">
+        <v>5</v>
+      </c>
+      <c r="T387">
+        <v>0</v>
+      </c>
+      <c r="U387">
+        <v>0</v>
+      </c>
+      <c r="V387">
+        <v>5</v>
+      </c>
+      <c r="W387">
+        <v>1</v>
+      </c>
+      <c r="X387">
+        <v>0</v>
+      </c>
+      <c r="Y387">
+        <v>0</v>
+      </c>
+      <c r="Z387">
+        <v>0</v>
+      </c>
+      <c r="AA387">
+        <v>0</v>
+      </c>
+      <c r="AB387">
+        <v>0</v>
+      </c>
+      <c r="AC387">
+        <v>0</v>
+      </c>
+      <c r="AD387">
+        <v>0</v>
+      </c>
+      <c r="AE387">
+        <v>0</v>
+      </c>
+      <c r="AF387">
+        <v>1</v>
+      </c>
+      <c r="AG387">
+        <v>0</v>
+      </c>
+      <c r="AH387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A388">
+        <v>2026</v>
+      </c>
+      <c r="B388" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C388">
+        <v>9</v>
+      </c>
+      <c r="D388" t="s">
+        <v>76</v>
+      </c>
+      <c r="E388" t="str">
+        <f>VLOOKUP(D388,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F388" t="s">
+        <v>13</v>
+      </c>
+      <c r="G388">
+        <v>6</v>
+      </c>
+      <c r="H388">
+        <v>2</v>
+      </c>
+      <c r="I388">
+        <v>3</v>
+      </c>
+      <c r="J388" t="s">
+        <v>32</v>
+      </c>
+      <c r="K388" t="s">
+        <v>31</v>
+      </c>
+      <c r="L388">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="M388">
+        <v>4</v>
+      </c>
+      <c r="N388">
+        <v>4</v>
+      </c>
+      <c r="O388">
+        <v>10</v>
+      </c>
+      <c r="P388">
+        <v>8</v>
+      </c>
+      <c r="Q388">
+        <v>4</v>
+      </c>
+      <c r="R388">
+        <v>4</v>
+      </c>
+      <c r="S388">
+        <v>0</v>
+      </c>
+      <c r="T388">
+        <v>5</v>
+      </c>
+      <c r="U388">
+        <v>0</v>
+      </c>
+      <c r="V388">
+        <v>0</v>
+      </c>
+      <c r="W388">
+        <v>0</v>
+      </c>
+      <c r="X388">
+        <v>0</v>
+      </c>
+      <c r="Y388">
+        <v>0</v>
+      </c>
+      <c r="Z388">
+        <v>0</v>
+      </c>
+      <c r="AA388">
+        <v>0</v>
+      </c>
+      <c r="AB388">
+        <v>0</v>
+      </c>
+      <c r="AC388">
+        <v>0</v>
+      </c>
+      <c r="AD388">
+        <v>1</v>
+      </c>
+      <c r="AE388">
+        <v>0</v>
+      </c>
+      <c r="AF388">
+        <v>0</v>
+      </c>
+      <c r="AG388">
+        <v>0</v>
+      </c>
+      <c r="AH388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A389">
+        <v>2026</v>
+      </c>
+      <c r="B389" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C389">
+        <v>9</v>
+      </c>
+      <c r="D389" t="s">
+        <v>76</v>
+      </c>
+      <c r="E389" t="str">
+        <f>VLOOKUP(D389,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F389" t="s">
+        <v>12</v>
+      </c>
+      <c r="G389">
+        <v>8</v>
+      </c>
+      <c r="H389">
+        <v>2</v>
+      </c>
+      <c r="I389">
+        <v>2</v>
+      </c>
+      <c r="J389" t="s">
+        <v>37</v>
+      </c>
+      <c r="K389" t="s">
+        <v>31</v>
+      </c>
+      <c r="L389">
+        <f t="shared" si="9"/>
+        <v>35</v>
+      </c>
+      <c r="M389">
+        <v>5</v>
+      </c>
+      <c r="N389">
+        <v>4</v>
+      </c>
+      <c r="O389">
+        <v>3</v>
+      </c>
+      <c r="P389">
+        <v>7</v>
+      </c>
+      <c r="Q389">
+        <v>9</v>
+      </c>
+      <c r="R389">
+        <v>4</v>
+      </c>
+      <c r="S389">
+        <v>0</v>
+      </c>
+      <c r="T389">
+        <v>3</v>
+      </c>
+      <c r="U389">
+        <v>0</v>
+      </c>
+      <c r="V389">
+        <v>9</v>
+      </c>
+      <c r="W389">
+        <v>0</v>
+      </c>
+      <c r="X389">
+        <v>0</v>
+      </c>
+      <c r="Y389">
+        <v>0</v>
+      </c>
+      <c r="Z389">
+        <v>0</v>
+      </c>
+      <c r="AA389">
+        <v>0</v>
+      </c>
+      <c r="AB389">
+        <v>0</v>
+      </c>
+      <c r="AC389">
+        <v>0</v>
+      </c>
+      <c r="AD389">
+        <v>0</v>
+      </c>
+      <c r="AE389">
+        <v>0</v>
+      </c>
+      <c r="AF389">
+        <v>0</v>
+      </c>
+      <c r="AG389">
+        <v>0</v>
+      </c>
+      <c r="AH389">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AP377" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
-  <dataValidations disablePrompts="1" count="1">
+  <autoFilter ref="A2:AP389" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}"/>
+  <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:AB8 W3:X41 Y9:Z41 W44:Z56 X58:Z116 X117:AB119 X120:Z122 X123:AB128 W58:W175 X129:Z175 W177:Z223 W225:Z299 W301:Z302 W304:Z1048576" xr:uid="{0D054DE4-3D8E-4484-9FF1-661236EA2207}">
       <formula1>0</formula1>
       <formula2>1</formula2>
@@ -40744,7 +41380,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{761EF6A8-1D47-4E5D-B2B8-225F6EE4B0A2}">
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$3</xm:f>

--- a/catan_data.xlsx
+++ b/catan_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88b1f18c208c1b3c/Documents/CatanData/catan_data/catan_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C07282-3C17-4968-8D8D-AB0CA1D5EC3C}"/>
+  <xr:revisionPtr revIDLastSave="956" documentId="13_ncr:1_{0CE434BB-4BBF-4ED1-8FB9-9E48A15C8776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C47A2FE1-F0D0-4FCF-8A3F-D24FF46771D7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="15260" xr2:uid="{83B30B11-FE95-4925-9DB4-CCB67C570BD6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="79">
   <si>
     <t>season</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8635BA-0A9D-4832-9FDC-B5CDD32D9D6C}">
-  <dimension ref="A1:AP389"/>
+  <dimension ref="A1:AP392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -38860,7 +38860,7 @@
         <v>31</v>
       </c>
       <c r="L366">
-        <f t="shared" ref="L366:L389" si="9">SUM(O366:V366)</f>
+        <f t="shared" ref="L366:L392" si="9">SUM(O366:V366)</f>
         <v>33</v>
       </c>
       <c r="M366">
@@ -41365,6 +41365,324 @@
         <v>0</v>
       </c>
       <c r="AH389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A390">
+        <v>2026</v>
+      </c>
+      <c r="B390" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C390">
+        <v>10</v>
+      </c>
+      <c r="D390" t="s">
+        <v>76</v>
+      </c>
+      <c r="E390" t="str">
+        <f>VLOOKUP(D390,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F390" t="s">
+        <v>13</v>
+      </c>
+      <c r="G390">
+        <v>4</v>
+      </c>
+      <c r="H390">
+        <v>0</v>
+      </c>
+      <c r="I390">
+        <v>3</v>
+      </c>
+      <c r="J390" t="s">
+        <v>36</v>
+      </c>
+      <c r="K390" t="s">
+        <v>31</v>
+      </c>
+      <c r="L390">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="M390">
+        <v>5</v>
+      </c>
+      <c r="N390">
+        <v>5</v>
+      </c>
+      <c r="O390">
+        <v>3</v>
+      </c>
+      <c r="P390">
+        <v>11</v>
+      </c>
+      <c r="Q390">
+        <v>4</v>
+      </c>
+      <c r="R390">
+        <v>3</v>
+      </c>
+      <c r="S390">
+        <v>2</v>
+      </c>
+      <c r="T390">
+        <v>3</v>
+      </c>
+      <c r="U390">
+        <v>2</v>
+      </c>
+      <c r="V390">
+        <v>0</v>
+      </c>
+      <c r="W390">
+        <v>0</v>
+      </c>
+      <c r="X390">
+        <v>0</v>
+      </c>
+      <c r="Y390">
+        <v>0</v>
+      </c>
+      <c r="Z390">
+        <v>0</v>
+      </c>
+      <c r="AA390">
+        <v>0</v>
+      </c>
+      <c r="AB390">
+        <v>0</v>
+      </c>
+      <c r="AC390">
+        <v>1</v>
+      </c>
+      <c r="AD390">
+        <v>0</v>
+      </c>
+      <c r="AE390">
+        <v>0</v>
+      </c>
+      <c r="AF390">
+        <v>0</v>
+      </c>
+      <c r="AG390">
+        <v>0</v>
+      </c>
+      <c r="AH390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A391">
+        <v>2026</v>
+      </c>
+      <c r="B391" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C391">
+        <v>10</v>
+      </c>
+      <c r="D391" t="s">
+        <v>76</v>
+      </c>
+      <c r="E391" t="str">
+        <f>VLOOKUP(D391,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F391" t="s">
+        <v>11</v>
+      </c>
+      <c r="G391">
+        <v>9</v>
+      </c>
+      <c r="H391">
+        <v>3</v>
+      </c>
+      <c r="I391">
+        <v>2</v>
+      </c>
+      <c r="J391" t="s">
+        <v>32</v>
+      </c>
+      <c r="K391" t="s">
+        <v>31</v>
+      </c>
+      <c r="L391">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="M391">
+        <v>5</v>
+      </c>
+      <c r="N391">
+        <v>4</v>
+      </c>
+      <c r="O391">
+        <v>8</v>
+      </c>
+      <c r="P391">
+        <v>4</v>
+      </c>
+      <c r="Q391">
+        <v>8</v>
+      </c>
+      <c r="R391">
+        <v>0</v>
+      </c>
+      <c r="S391">
+        <v>3</v>
+      </c>
+      <c r="T391">
+        <v>3</v>
+      </c>
+      <c r="U391">
+        <v>0</v>
+      </c>
+      <c r="V391">
+        <v>4</v>
+      </c>
+      <c r="W391">
+        <v>0</v>
+      </c>
+      <c r="X391">
+        <v>0</v>
+      </c>
+      <c r="Y391">
+        <v>0</v>
+      </c>
+      <c r="Z391">
+        <v>0</v>
+      </c>
+      <c r="AA391">
+        <v>0</v>
+      </c>
+      <c r="AB391">
+        <v>0</v>
+      </c>
+      <c r="AC391">
+        <v>0</v>
+      </c>
+      <c r="AD391">
+        <v>0</v>
+      </c>
+      <c r="AE391">
+        <v>0</v>
+      </c>
+      <c r="AF391">
+        <v>0</v>
+      </c>
+      <c r="AG391">
+        <v>1</v>
+      </c>
+      <c r="AH391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A392">
+        <v>2026</v>
+      </c>
+      <c r="B392" s="5">
+        <v>46206</v>
+      </c>
+      <c r="C392">
+        <v>10</v>
+      </c>
+      <c r="D392" t="s">
+        <v>76</v>
+      </c>
+      <c r="E392" t="str">
+        <f>VLOOKUP(D392,Sheet2!$I$1:$J$12,2,FALSE)</f>
+        <v>53.5953349871887, 9.982308366971944</v>
+      </c>
+      <c r="F392" t="s">
+        <v>12</v>
+      </c>
+      <c r="G392">
+        <v>13</v>
+      </c>
+      <c r="H392">
+        <v>4</v>
+      </c>
+      <c r="I392">
+        <v>1</v>
+      </c>
+      <c r="J392" t="s">
+        <v>37</v>
+      </c>
+      <c r="K392" t="s">
+        <v>31</v>
+      </c>
+      <c r="L392">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="M392">
+        <v>4</v>
+      </c>
+      <c r="N392">
+        <v>3</v>
+      </c>
+      <c r="O392">
+        <v>12</v>
+      </c>
+      <c r="P392">
+        <v>0</v>
+      </c>
+      <c r="Q392">
+        <v>4</v>
+      </c>
+      <c r="R392">
+        <v>0</v>
+      </c>
+      <c r="S392">
+        <v>8</v>
+      </c>
+      <c r="T392">
+        <v>12</v>
+      </c>
+      <c r="U392">
+        <v>0</v>
+      </c>
+      <c r="V392">
+        <v>0</v>
+      </c>
+      <c r="W392">
+        <v>0</v>
+      </c>
+      <c r="X392">
+        <v>0</v>
+      </c>
+      <c r="Y392">
+        <v>0</v>
+      </c>
+      <c r="Z392">
+        <v>0</v>
+      </c>
+      <c r="AA392">
+        <v>0</v>
+      </c>
+      <c r="AB392">
+        <v>0</v>
+      </c>
+      <c r="AC392">
+        <v>0</v>
+      </c>
+      <c r="AD392">
+        <v>0</v>
+      </c>
+      <c r="AE392">
+        <v>0</v>
+      </c>
+      <c r="AF392">
+        <v>0</v>
+      </c>
+      <c r="AG392">
+        <v>0</v>
+      </c>
+      <c r="AH392">
         <v>0</v>
       </c>
     </row>
